--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0001T0006Z000C1N33_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0001T0006Z000C1N33_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>71.08863514432073</v>
+        <v>11.55190321095212</v>
       </c>
       <c r="D2" t="n">
-        <v>71.0441258969684</v>
+        <v>11.54467045825736</v>
       </c>
       <c r="E2" t="n">
-        <v>16.37803198234985</v>
+        <v>2.661430197131851</v>
       </c>
       <c r="F2" t="n">
-        <v>16.36164766107249</v>
+        <v>2.65876774492428</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>33.07189566603335</v>
+        <v>5.37418304573042</v>
       </c>
       <c r="D3" t="n">
-        <v>32.41791929419532</v>
+        <v>5.26791188530674</v>
       </c>
       <c r="E3" t="n">
-        <v>16.37803198234985</v>
+        <v>2.661430197131851</v>
       </c>
       <c r="F3" t="n">
-        <v>16.36164766107249</v>
+        <v>2.65876774492428</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>54.57206310790095</v>
+        <v>8.867960255033905</v>
       </c>
       <c r="D4" t="n">
-        <v>54.54232981702013</v>
+        <v>8.863128595265772</v>
       </c>
       <c r="E4" t="n">
-        <v>16.37803198234985</v>
+        <v>2.661430197131851</v>
       </c>
       <c r="F4" t="n">
-        <v>16.36164766107249</v>
+        <v>2.65876774492428</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>42.11318006229719</v>
+        <v>6.843391760123294</v>
       </c>
       <c r="D5" t="n">
-        <v>41.70300791754764</v>
+        <v>6.776738786601491</v>
       </c>
       <c r="E5" t="n">
-        <v>16.37803198234985</v>
+        <v>2.661430197131851</v>
       </c>
       <c r="F5" t="n">
-        <v>16.36164766107249</v>
+        <v>2.65876774492428</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>57.51692494790627</v>
+        <v>9.34650030403477</v>
       </c>
       <c r="D6" t="n">
-        <v>57.49892263357864</v>
+        <v>9.34357492795653</v>
       </c>
       <c r="E6" t="n">
-        <v>16.37803198234985</v>
+        <v>2.661430197131851</v>
       </c>
       <c r="F6" t="n">
-        <v>16.36164766107249</v>
+        <v>2.65876774492428</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>61.67395541247178</v>
+        <v>10.02201775452666</v>
       </c>
       <c r="D7" t="n">
-        <v>61.66659491599932</v>
+        <v>10.02082167384989</v>
       </c>
       <c r="E7" t="n">
-        <v>16.37803198234985</v>
+        <v>2.661430197131851</v>
       </c>
       <c r="F7" t="n">
-        <v>16.36164766107249</v>
+        <v>2.65876774492428</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>12.08767364513886</v>
+        <v>1.964246967335066</v>
       </c>
       <c r="D8" t="n">
-        <v>11.86839295420762</v>
+        <v>1.928613855058738</v>
       </c>
       <c r="E8" t="n">
-        <v>16.37803198234985</v>
+        <v>2.661430197131851</v>
       </c>
       <c r="F8" t="n">
-        <v>16.36164766107249</v>
+        <v>2.65876774492428</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>22.98825263318348</v>
+        <v>3.735591052892315</v>
       </c>
       <c r="D9" t="n">
-        <v>24.09451431347711</v>
+        <v>3.91535857594003</v>
       </c>
       <c r="E9" t="n">
-        <v>16.37803198234985</v>
+        <v>2.661430197131851</v>
       </c>
       <c r="F9" t="n">
-        <v>16.36164766107249</v>
+        <v>2.65876774492428</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>38.28640560012486</v>
+        <v>6.221540910020289</v>
       </c>
       <c r="D10" t="n">
-        <v>39.28527746249711</v>
+        <v>6.383857587655781</v>
       </c>
       <c r="E10" t="n">
-        <v>16.37803198234985</v>
+        <v>2.661430197131851</v>
       </c>
       <c r="F10" t="n">
-        <v>16.36164766107249</v>
+        <v>2.65876774492428</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>57.12894750280627</v>
+        <v>9.283453969206018</v>
       </c>
       <c r="D11" t="n">
-        <v>58.23756010728667</v>
+        <v>9.463603517434084</v>
       </c>
       <c r="E11" t="n">
-        <v>16.37803198234985</v>
+        <v>2.661430197131851</v>
       </c>
       <c r="F11" t="n">
-        <v>16.36164766107249</v>
+        <v>2.65876774492428</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>54.49707323015174</v>
+        <v>8.855774399899659</v>
       </c>
       <c r="D12" t="n">
-        <v>54.52164286591388</v>
+        <v>8.859766965711007</v>
       </c>
       <c r="E12" t="n">
-        <v>16.37803198234985</v>
+        <v>2.661430197131851</v>
       </c>
       <c r="F12" t="n">
-        <v>16.36164766107249</v>
+        <v>2.65876774492428</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>50.62309465194078</v>
+        <v>8.226252880940377</v>
       </c>
       <c r="D13" t="n">
-        <v>50.68608834744586</v>
+        <v>8.236489356459952</v>
       </c>
       <c r="E13" t="n">
-        <v>16.37803198234985</v>
+        <v>2.661430197131851</v>
       </c>
       <c r="F13" t="n">
-        <v>16.36164766107249</v>
+        <v>2.65876774492428</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
